--- a/output/StructureDefinition-ReferenciaDocumental.xlsx
+++ b/output/StructureDefinition-ReferenciaDocumental.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$99</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3913" uniqueCount="661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3991" uniqueCount="672">
   <si>
     <t>Property</t>
   </si>
@@ -27,13 +27,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://mhd.ri.hsisalud.org/StructureDefinition/ReferenciaDocumental</t>
+    <t>https://hl7chile.cl/fhir/ig/mhd/StructureDefinition/ReferenciaDocumental</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,25 +57,25 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:42:41-04:00</t>
+    <t>2026-10-15T12:40:59-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>HSI Pladema</t>
+    <t>Hl7 Chile</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>HSI Pladema (https://hsi.pladema.net)</t>
+    <t>Hl7 Chile (https://hl7chile.cl/)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Argentina</t>
+    <t>Chile</t>
   </si>
   <si>
     <t>Description</t>
@@ -457,7 +457,7 @@
     <t>DocumentReference.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -498,7 +498,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -522,7 +522,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -565,7 +565,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -626,19 +626,39 @@
     <t>DocumentReference.extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
+    <t>DocumentReference.extension:homeCommunityId</t>
+  </si>
+  <si>
+    <t>homeCommunityId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://profiles.ihe.net/ITI/MHD/StructureDefinition/ihe-HomeCommunityId}
+</t>
+  </si>
+  <si>
+    <t>The homeCommunityId where the artifact resides</t>
+  </si>
+  <si>
+    <t>The globally unique, immutable, identifier of the homeCommunityId entity where this artifact resides. The format of the value is an OID.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>DocumentEntry.homeCommunityId</t>
+  </si>
+  <si>
     <t>DocumentReference.modifierExtension</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -669,17 +689,25 @@
 &lt;/valueIdentifier&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>DocumentEntry.uniqueId</t>
   </si>
   <si>
-    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
-  </si>
-  <si>
-    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
+    <t>Event.identifier</t>
+  </si>
+  <si>
+    <t>Composition.identifier</t>
+  </si>
+  <si>
+    <t>.id</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/id</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>TXA-12</t>
   </si>
   <si>
     <t>DocumentReference.identifier</t>
@@ -695,20 +723,14 @@
     <t>Identificador alternativo para el documento IPS nacional referenciado. Se usa comunmente cuando el document se ha almacenado en varios dominios, y cada uno de ellos le ha asignado un identificador diferente.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:use}
+    <t xml:space="preserve">value:type}
 </t>
   </si>
   <si>
     <t>DocumentEntry.entryUUID</t>
   </si>
   <si>
-    <t>Event.identifier</t>
-  </si>
-  <si>
     <t>.id / .setId</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
   </si>
   <si>
     <t>TXA-16?</t>
@@ -724,10 +746,22 @@
 </t>
   </si>
   <si>
-    <t>An identifier intended for computation</t>
-  </si>
-  <si>
-    <t>An identifier - identifies some entity uniquely and unambiguously. Typically this is used for business identifiers.</t>
+    <t>Business identifier for the DocumentReference</t>
+  </si>
+  <si>
+    <t>The Business identifier for the DocumentReference which maps to the DocumentEntry.entryUUID in XDS. This is used to refer to the DocumentReference itself as a record of the Document's metadata, as opposed to the UniqueId element which identifies the document which is pointed at by the document reference.</t>
+  </si>
+  <si>
+    <t>DocumentReference.identifier:uniqueId</t>
+  </si>
+  <si>
+    <t>uniqueId</t>
+  </si>
+  <si>
+    <t>Unique identifier for the referenced Document</t>
+  </si>
+  <si>
+    <t>The unique identifier for the referenced Document which maps to the DocumentEntry.uniqueId in XDS. This is used to identify the document which is pointed at by the DocumentReference Resource, as opposed to the entryUUID element which identifies the DocumentReference Resource itself. If this is present, then the identifier SHALL be the same as the one found in masterIdentifier.</t>
   </si>
   <si>
     <t>DocumentReference.status</t>
@@ -807,7 +841,7 @@
     <t>Key metadata element describing the document that describes he exact type of document. Helps humans to assess whether the document is of interest when viewing a list of documents.</t>
   </si>
   <si>
-    <t>http://mhd.ri.hsisalud.org/ValueSet/VSTipoDocumento</t>
+    <t>https://hl7chile.cl/fhir/ig/mhd/ValueSet/VSTipoDocumento</t>
   </si>
   <si>
     <t>DocumentEntry.typeCode</t>
@@ -1032,7 +1066,7 @@
     <t>Key metadata element describing the the category or classification of the document. This is a broader perspective that groups similar documents based on how they would be used. This is a primary key used in searching.</t>
   </si>
   <si>
-    <t>http://mhd.ri.hsisalud.org/ValueSet/VSCategoriaDoc</t>
+    <t>https://hl7chile.cl/fhir/ig/mhd/ValueSet/VSCategoriaDoc</t>
   </si>
   <si>
     <t>DocumentEntry.classCode</t>
@@ -1095,7 +1129,7 @@
     <t>DocumentReference.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://ips.ri.hsisalud.org/StructureDefinition/PacienteArg)
+    <t xml:space="preserve">Reference(https://hl7chile.cl/fhir/ig/clcore/StructureDefinition/CorePacienteCl)
 </t>
   </si>
   <si>
@@ -1157,7 +1191,7 @@
     <t>DocumentReference.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|Device|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|Device|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1191,7 +1225,7 @@
     <t>DocumentReference.authenticator</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1225,7 +1259,7 @@
     <t>DocumentReference.custodian</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1331,7 +1365,7 @@
     <t>DocumentReference.relatesTo.target</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1)
 </t>
   </si>
   <si>
@@ -1578,7 +1612,7 @@
     <t>Attachment.url</t>
   </si>
   <si>
-    <t>DocumentEntry.repositoryUniqueId or DocuemntEntry.URI</t>
+    <t>DocumentEntry.repositoryUniqueId+DocumentEntry.uniqueId or DocumentEntry.URI</t>
   </si>
   <si>
     <t>./reference/literal</t>
@@ -1736,7 +1770,7 @@
     <t>DocumentReference.context.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare)
+    <t xml:space="preserve">Reference(Encounter|4.0.1|EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
@@ -1842,7 +1876,7 @@
 </t>
   </si>
   <si>
-    <t>DocumetEntry.serviceStartTime</t>
+    <t>DocumentEntry.serviceStartTime</t>
   </si>
   <si>
     <t>./low</t>
@@ -1890,7 +1924,7 @@
     <t>XDS Facility Type.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/c80-facilitycodes</t>
+    <t>http://hl7.org/fhir/ValueSet/c80-facilitycodes|4.0.1</t>
   </si>
   <si>
     <t>DocumentEntry.healthcareFacilityTypeCode</t>
@@ -1923,7 +1957,7 @@
     <t>Additional details about where the content was created (e.g. clinical specialty).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes|4.0.1</t>
   </si>
   <si>
     <t>DocumentEntry.practiceSettingCode</t>
@@ -1932,7 +1966,7 @@
     <t>DocumentReference.context.sourcePatientInfo</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient)
+    <t xml:space="preserve">Reference(Patient|4.0.1)
 </t>
   </si>
   <si>
@@ -1989,7 +2023,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -2037,7 +2071,7 @@
     <t>DocumentReference.context.related</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -2377,20 +2411,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR97"/>
+  <dimension ref="A1:AR99"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="47.13671875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="47.13671875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="9.984375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.55078125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="45.96875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="45.96875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="15.91015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="77.14453125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="93.98828125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2399,30 +2433,30 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="48.1796875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="85.89453125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="56.0234375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="38.8203125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="8.51953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="8.859375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="47.203125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="53.2734375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="37.78125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="70.00390625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="23.9609375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="45.70703125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="68.71875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="44.5859375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="29.45703125" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="73.5859375" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="141.66015625" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="72.20703125" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="139.26953125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4454,7 +4488,7 @@
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4476,14 +4510,12 @@
         <v>115</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>116</v>
+        <v>196</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>118</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>80</v>
@@ -4520,19 +4552,17 @@
         <v>80</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="AC17" s="2"/>
       <c r="AD17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4556,7 +4586,7 @@
         <v>80</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>194</v>
+        <v>80</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>80</v>
@@ -4573,12 +4603,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>200</v>
+      </c>
       <c r="D18" t="s" s="2">
         <v>80</v>
       </c>
@@ -4587,25 +4619,25 @@
         <v>81</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>115</v>
+        <v>201</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4656,7 +4688,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4665,13 +4697,13 @@
         <v>82</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>80</v>
+        <v>204</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>123</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>80</v>
+        <v>205</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>80</v>
@@ -4695,12 +4727,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4708,35 +4740,31 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I19" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="I19" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="J19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>203</v>
+        <v>115</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>80</v>
       </c>
@@ -4748,87 +4776,87 @@
         <v>80</v>
       </c>
       <c r="T19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="AK19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AR19" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="U19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AG19" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI19" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="AJ19" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK19" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ19" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="AR19" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" hidden="true">
-      <c r="A20" t="s" s="2">
-        <v>213</v>
-      </c>
       <c r="B20" t="s" s="2">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4836,10 +4864,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>95</v>
@@ -4851,16 +4879,20 @@
         <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>80</v>
       </c>
@@ -4872,7 +4904,7 @@
         <v>80</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>80</v>
+        <v>214</v>
       </c>
       <c r="U20" t="s" s="2">
         <v>80</v>
@@ -4896,23 +4928,25 @@
         <v>80</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AC20" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>80</v>
@@ -4921,40 +4955,38 @@
         <v>106</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AL20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="AM20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AP20" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AO20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP20" t="s" s="2">
+      <c r="AQ20" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AQ20" t="s" s="2">
+      <c r="AR20" t="s" s="2">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="21" hidden="true">
+      <c r="A21" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="AR20" t="s" s="2">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>223</v>
-      </c>
       <c r="B21" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>80</v>
       </c>
@@ -4972,16 +5004,16 @@
         <v>80</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="L21" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -5020,19 +5052,17 @@
         <v>80</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="AC21" s="2"/>
       <c r="AD21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -5041,50 +5071,52 @@
         <v>82</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>209</v>
+        <v>80</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>80</v>
+        <v>227</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>80</v>
+        <v>216</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>80</v>
+        <v>220</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>80</v>
+        <v>227</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="D22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>94</v>
@@ -5093,23 +5125,21 @@
         <v>95</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>171</v>
+        <v>232</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -5134,11 +5164,13 @@
         <v>80</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="Y22" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z22" t="s" s="2">
-        <v>233</v>
+        <v>80</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>80</v>
@@ -5156,13 +5188,13 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>80</v>
@@ -5171,38 +5203,40 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>234</v>
+        <v>80</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AO22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP22" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AQ22" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AR22" t="s" s="2">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="AM22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN22" t="s" s="2">
+      <c r="B23" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="C23" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="AO22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="AQ22" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="AR22" t="s" s="2">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="23" hidden="true">
-      <c r="A23" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>80</v>
       </c>
@@ -5211,10 +5245,10 @@
         <v>81</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>80</v>
@@ -5223,17 +5257,15 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>171</v>
+        <v>209</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>80</v>
@@ -5258,13 +5290,13 @@
         <v>80</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>232</v>
+        <v>80</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>243</v>
+        <v>80</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>244</v>
+        <v>80</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>80</v>
@@ -5282,13 +5314,13 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>80</v>
@@ -5300,33 +5332,33 @@
         <v>80</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>80</v>
+        <v>216</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>245</v>
+        <v>80</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>80</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5343,22 +5375,22 @@
         <v>95</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>249</v>
+        <v>171</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5384,11 +5416,11 @@
         <v>80</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>153</v>
+        <v>243</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>80</v>
@@ -5406,10 +5438,10 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>94</v>
@@ -5421,36 +5453,36 @@
         <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>256</v>
+        <v>80</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>258</v>
+        <v>80</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>261</v>
+        <v>245</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5461,7 +5493,7 @@
         <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>80</v>
@@ -5470,18 +5502,20 @@
         <v>80</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>108</v>
+        <v>171</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>109</v>
+        <v>251</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -5506,13 +5540,13 @@
         <v>80</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>80</v>
+        <v>243</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>80</v>
+        <v>254</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>80</v>
+        <v>255</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>80</v>
@@ -5530,7 +5564,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>111</v>
+        <v>250</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5542,7 +5576,7 @@
         <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>80</v>
@@ -5551,62 +5585,62 @@
         <v>80</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>80</v>
+        <v>256</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>112</v>
+        <v>257</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>80</v>
+        <v>248</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>80</v>
+        <v>258</v>
       </c>
       <c r="AR25" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>115</v>
+        <v>260</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>116</v>
+        <v>261</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>117</v>
+        <v>262</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>118</v>
+        <v>263</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5632,75 +5666,73 @@
         <v>80</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>122</v>
+        <v>259</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>80</v>
+        <v>265</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>80</v>
+        <v>266</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>80</v>
+        <v>267</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>80</v>
+        <v>269</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>80</v>
+        <v>270</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>80</v>
+        <v>271</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>80</v>
+        <v>272</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5711,7 +5743,7 @@
         <v>81</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>80</v>
@@ -5720,23 +5752,19 @@
         <v>80</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>149</v>
+        <v>108</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>265</v>
+        <v>109</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>80</v>
       </c>
@@ -5784,19 +5812,19 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>269</v>
+        <v>111</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>80</v>
@@ -5808,7 +5836,7 @@
         <v>80</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>270</v>
+        <v>112</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>80</v>
@@ -5817,7 +5845,7 @@
         <v>80</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>271</v>
+        <v>80</v>
       </c>
       <c r="AR27" t="s" s="2">
         <v>80</v>
@@ -5825,21 +5853,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>80</v>
@@ -5851,15 +5879,17 @@
         <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>117</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>80</v>
@@ -5896,31 +5926,31 @@
         <v>80</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>80</v>
+        <v>123</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>80</v>
@@ -5949,14 +5979,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5972,21 +6002,23 @@
         <v>80</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>115</v>
+        <v>149</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>116</v>
+        <v>276</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>117</v>
+        <v>277</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>80</v>
       </c>
@@ -6022,19 +6054,19 @@
         <v>80</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>122</v>
+        <v>280</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -6046,7 +6078,7 @@
         <v>80</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>80</v>
@@ -6058,7 +6090,7 @@
         <v>80</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>112</v>
+        <v>281</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>80</v>
@@ -6067,7 +6099,7 @@
         <v>80</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>80</v>
+        <v>282</v>
       </c>
       <c r="AR29" t="s" s="2">
         <v>80</v>
@@ -6075,10 +6107,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6098,23 +6130,19 @@
         <v>80</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>275</v>
+        <v>109</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>278</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>80</v>
       </c>
@@ -6126,7 +6154,7 @@
         <v>80</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>279</v>
+        <v>80</v>
       </c>
       <c r="U30" t="s" s="2">
         <v>80</v>
@@ -6162,7 +6190,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>280</v>
+        <v>111</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -6174,7 +6202,7 @@
         <v>80</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>80</v>
@@ -6186,7 +6214,7 @@
         <v>80</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>281</v>
+        <v>112</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>80</v>
@@ -6195,7 +6223,7 @@
         <v>80</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>282</v>
+        <v>80</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>80</v>
@@ -6203,21 +6231,21 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>80</v>
@@ -6226,19 +6254,19 @@
         <v>80</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>284</v>
+        <v>116</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>285</v>
+        <v>117</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>286</v>
+        <v>118</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6276,31 +6304,31 @@
         <v>80</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>287</v>
+        <v>122</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>80</v>
@@ -6312,7 +6340,7 @@
         <v>80</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>288</v>
+        <v>112</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>80</v>
@@ -6321,7 +6349,7 @@
         <v>80</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>289</v>
+        <v>80</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>80</v>
@@ -6329,10 +6357,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6355,17 +6383,19 @@
         <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>171</v>
+        <v>136</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="O32" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>80</v>
@@ -6378,7 +6408,7 @@
         <v>80</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="U32" t="s" s="2">
         <v>80</v>
@@ -6414,7 +6444,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6438,7 +6468,7 @@
         <v>80</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>257</v>
+        <v>292</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>80</v>
@@ -6447,7 +6477,7 @@
         <v>80</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>80</v>
@@ -6455,10 +6485,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6484,15 +6514,15 @@
         <v>108</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" t="s" s="2">
-        <v>300</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>80</v>
       </c>
@@ -6504,7 +6534,7 @@
         <v>80</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>301</v>
+        <v>80</v>
       </c>
       <c r="U33" t="s" s="2">
         <v>80</v>
@@ -6540,7 +6570,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6564,7 +6594,7 @@
         <v>80</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>80</v>
@@ -6573,7 +6603,7 @@
         <v>80</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>80</v>
@@ -6581,10 +6611,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6607,19 +6637,17 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>306</v>
+        <v>171</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>80</v>
@@ -6632,7 +6660,7 @@
         <v>80</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>80</v>
+        <v>305</v>
       </c>
       <c r="U34" t="s" s="2">
         <v>80</v>
@@ -6668,7 +6696,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6692,7 +6720,7 @@
         <v>80</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>312</v>
+        <v>268</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>80</v>
@@ -6701,7 +6729,7 @@
         <v>80</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>80</v>
@@ -6709,10 +6737,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6738,16 +6766,14 @@
         <v>108</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>80</v>
@@ -6760,7 +6786,7 @@
         <v>80</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>80</v>
+        <v>312</v>
       </c>
       <c r="U35" t="s" s="2">
         <v>80</v>
@@ -6796,7 +6822,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6820,7 +6846,7 @@
         <v>80</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>80</v>
@@ -6829,32 +6855,32 @@
         <v>80</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>323</v>
+        <v>80</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>80</v>
@@ -6863,18 +6889,20 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>249</v>
+        <v>317</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
       </c>
@@ -6898,11 +6926,13 @@
         <v>80</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y36" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z36" t="s" s="2">
-        <v>327</v>
+        <v>80</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>80</v>
@@ -6926,7 +6956,7 @@
         <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>80</v>
@@ -6935,36 +6965,36 @@
         <v>106</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>328</v>
+        <v>80</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>329</v>
+        <v>80</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>331</v>
+        <v>80</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>259</v>
+        <v>80</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>80</v>
+        <v>324</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>332</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6984,19 +7014,23 @@
         <v>80</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
         <v>108</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>109</v>
+        <v>326</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>327</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>329</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
       </c>
@@ -7044,7 +7078,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>111</v>
+        <v>330</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -7056,7 +7090,7 @@
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>80</v>
@@ -7068,7 +7102,7 @@
         <v>80</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>112</v>
+        <v>331</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>80</v>
@@ -7077,50 +7111,50 @@
         <v>80</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>80</v>
+        <v>332</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>114</v>
+        <v>334</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>115</v>
+        <v>260</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>116</v>
+        <v>335</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>117</v>
+        <v>336</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>118</v>
+        <v>337</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7146,31 +7180,29 @@
         <v>80</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>80</v>
+        <v>338</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>122</v>
+        <v>333</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -7182,39 +7214,39 @@
         <v>80</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>80</v>
+        <v>339</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>80</v>
+        <v>340</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>112</v>
+        <v>341</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>80</v>
+        <v>342</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>80</v>
+        <v>270</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>80</v>
+        <v>343</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7225,7 +7257,7 @@
         <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>80</v>
@@ -7234,23 +7266,19 @@
         <v>80</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>149</v>
+        <v>108</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>265</v>
+        <v>109</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>80</v>
       </c>
@@ -7298,19 +7326,19 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>269</v>
+        <v>111</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>80</v>
@@ -7322,7 +7350,7 @@
         <v>80</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>270</v>
+        <v>112</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>80</v>
@@ -7331,7 +7359,7 @@
         <v>80</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>271</v>
+        <v>80</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>80</v>
@@ -7339,21 +7367,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>80</v>
@@ -7365,15 +7393,17 @@
         <v>80</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>117</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>80</v>
@@ -7410,31 +7440,31 @@
         <v>80</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>80</v>
+        <v>123</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>80</v>
@@ -7463,14 +7493,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7486,21 +7516,23 @@
         <v>80</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>115</v>
+        <v>149</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>116</v>
+        <v>276</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>117</v>
+        <v>277</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
       </c>
@@ -7536,19 +7568,19 @@
         <v>80</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>122</v>
+        <v>280</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7560,7 +7592,7 @@
         <v>80</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>80</v>
@@ -7572,7 +7604,7 @@
         <v>80</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>112</v>
+        <v>281</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>80</v>
@@ -7581,7 +7613,7 @@
         <v>80</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>80</v>
+        <v>282</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>80</v>
@@ -7589,10 +7621,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7612,23 +7644,19 @@
         <v>80</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>275</v>
+        <v>109</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>278</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>80</v>
       </c>
@@ -7640,7 +7668,7 @@
         <v>80</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>279</v>
+        <v>80</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>80</v>
@@ -7676,7 +7704,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>280</v>
+        <v>111</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7688,7 +7716,7 @@
         <v>80</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>80</v>
@@ -7700,7 +7728,7 @@
         <v>80</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>281</v>
+        <v>112</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>80</v>
@@ -7709,7 +7737,7 @@
         <v>80</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>282</v>
+        <v>80</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>80</v>
@@ -7717,21 +7745,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>80</v>
@@ -7740,19 +7768,19 @@
         <v>80</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>284</v>
+        <v>116</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>285</v>
+        <v>117</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>286</v>
+        <v>118</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7790,31 +7818,31 @@
         <v>80</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>287</v>
+        <v>122</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>80</v>
@@ -7826,7 +7854,7 @@
         <v>80</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>288</v>
+        <v>112</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>80</v>
@@ -7835,7 +7863,7 @@
         <v>80</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>289</v>
+        <v>80</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>80</v>
@@ -7843,10 +7871,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7869,17 +7897,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>171</v>
+        <v>136</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="O44" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>80</v>
@@ -7892,7 +7922,7 @@
         <v>80</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>341</v>
+        <v>290</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>80</v>
@@ -7928,7 +7958,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7952,7 +7982,7 @@
         <v>80</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>257</v>
+        <v>292</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>80</v>
@@ -7961,7 +7991,7 @@
         <v>80</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AR44" t="s" s="2">
         <v>80</v>
@@ -7969,10 +7999,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7998,15 +8028,15 @@
         <v>108</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" t="s" s="2">
-        <v>300</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>80</v>
       </c>
@@ -8018,7 +8048,7 @@
         <v>80</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>343</v>
+        <v>80</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>80</v>
@@ -8054,7 +8084,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -8078,7 +8108,7 @@
         <v>80</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>80</v>
@@ -8087,7 +8117,7 @@
         <v>80</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="AR45" t="s" s="2">
         <v>80</v>
@@ -8095,10 +8125,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8121,19 +8151,17 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>306</v>
+        <v>171</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>80</v>
@@ -8146,7 +8174,7 @@
         <v>80</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>80</v>
+        <v>352</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>80</v>
@@ -8182,7 +8210,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -8206,7 +8234,7 @@
         <v>80</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>312</v>
+        <v>268</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>80</v>
@@ -8215,7 +8243,7 @@
         <v>80</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>80</v>
@@ -8223,10 +8251,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8252,16 +8280,14 @@
         <v>108</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>80</v>
@@ -8271,10 +8297,10 @@
         <v>80</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>346</v>
+        <v>80</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>80</v>
+        <v>354</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>80</v>
@@ -8310,7 +8336,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8334,7 +8360,7 @@
         <v>80</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>80</v>
@@ -8343,18 +8369,18 @@
         <v>80</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8362,13 +8388,13 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>80</v>
@@ -8377,16 +8403,20 @@
         <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>348</v>
+        <v>317</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>349</v>
+        <v>318</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
       </c>
@@ -8434,7 +8464,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>347</v>
+        <v>322</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8449,50 +8479,50 @@
         <v>106</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>351</v>
+        <v>80</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>352</v>
+        <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>353</v>
+        <v>80</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>354</v>
+        <v>323</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>355</v>
+        <v>80</v>
       </c>
       <c r="AP48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ48" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AR48" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="49" hidden="true">
+      <c r="A49" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AQ48" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="AR48" t="s" s="2">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s" s="2">
-        <v>358</v>
-      </c>
       <c r="B49" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>359</v>
+        <v>80</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>80</v>
@@ -8501,18 +8531,20 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>360</v>
+        <v>326</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>361</v>
+        <v>327</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>329</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
       </c>
@@ -8521,7 +8553,7 @@
         <v>80</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>80</v>
+        <v>357</v>
       </c>
       <c r="T49" t="s" s="2">
         <v>80</v>
@@ -8560,7 +8592,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>358</v>
+        <v>330</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8578,22 +8610,22 @@
         <v>80</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>363</v>
+        <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>364</v>
+        <v>80</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>365</v>
+        <v>331</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>366</v>
+        <v>80</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>80</v>
+        <v>332</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>80</v>
@@ -8601,10 +8633,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8615,7 +8647,7 @@
         <v>94</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>95</v>
@@ -8627,17 +8659,15 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>371</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -8686,13 +8716,13 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>80</v>
@@ -8701,68 +8731,68 @@
         <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>80</v>
+        <v>367</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>372</v>
+        <v>362</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>80</v>
+        <v>370</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>379</v>
+        <v>130</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8812,7 +8842,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8827,36 +8857,36 @@
         <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>383</v>
+        <v>80</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>386</v>
+        <v>80</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>388</v>
+        <v>80</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>383</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8864,31 +8894,31 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8938,13 +8968,13 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>80</v>
@@ -8953,36 +8983,36 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>80</v>
+        <v>387</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>80</v>
+        <v>388</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>80</v>
+        <v>383</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8993,28 +9023,28 @@
         <v>81</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -9064,13 +9094,13 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>80</v>
@@ -9079,36 +9109,36 @@
         <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>80</v>
+        <v>384</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>80</v>
+        <v>397</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>80</v>
+        <v>398</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>80</v>
+        <v>399</v>
       </c>
       <c r="AR53" t="s" s="2">
-        <v>402</v>
+        <v>394</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9131,15 +9161,17 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>108</v>
+        <v>401</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>109</v>
+        <v>402</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>404</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>80</v>
@@ -9188,7 +9220,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>111</v>
+        <v>400</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -9200,19 +9232,19 @@
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>80</v>
+        <v>405</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>80</v>
+        <v>384</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>80</v>
+        <v>406</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>112</v>
+        <v>407</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>80</v>
@@ -9227,16 +9259,16 @@
         <v>80</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -9246,25 +9278,25 @@
         <v>82</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>115</v>
+        <v>409</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>116</v>
+        <v>410</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>117</v>
+        <v>411</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>118</v>
+        <v>412</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9314,7 +9346,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>122</v>
+        <v>408</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9326,19 +9358,19 @@
         <v>80</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>80</v>
+        <v>413</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>80</v>
+        <v>414</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>112</v>
+        <v>415</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>80</v>
@@ -9350,51 +9382,47 @@
         <v>80</v>
       </c>
       <c r="AR55" t="s" s="2">
-        <v>80</v>
+        <v>413</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>408</v>
+        <v>80</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>409</v>
+        <v>109</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>411</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>80</v>
       </c>
@@ -9442,19 +9470,19 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>412</v>
+        <v>111</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>80</v>
@@ -9466,7 +9494,7 @@
         <v>80</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>80</v>
@@ -9483,21 +9511,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>80</v>
@@ -9506,19 +9534,19 @@
         <v>80</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>171</v>
+        <v>115</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>414</v>
+        <v>116</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>415</v>
+        <v>117</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>416</v>
+        <v>118</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9544,13 +9572,13 @@
         <v>80</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>232</v>
+        <v>80</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>417</v>
+        <v>80</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>418</v>
+        <v>80</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>80</v>
@@ -9568,31 +9596,31 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>413</v>
+        <v>122</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>419</v>
+        <v>80</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>420</v>
+        <v>80</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>421</v>
+        <v>112</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>80</v>
@@ -9604,47 +9632,51 @@
         <v>80</v>
       </c>
       <c r="AR57" t="s" s="2">
-        <v>422</v>
+        <v>80</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>80</v>
+        <v>419</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="J58" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>424</v>
+        <v>115</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+        <v>421</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>422</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>80</v>
       </c>
@@ -9695,28 +9727,28 @@
         <v>423</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>427</v>
+        <v>80</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>428</v>
+        <v>80</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>429</v>
+        <v>194</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>80</v>
@@ -9728,15 +9760,15 @@
         <v>80</v>
       </c>
       <c r="AR58" t="s" s="2">
-        <v>430</v>
+        <v>80</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9744,7 +9776,7 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>94</v>
@@ -9759,20 +9791,18 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>108</v>
+        <v>171</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>435</v>
-      </c>
+        <v>427</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>80</v>
       </c>
@@ -9796,13 +9826,13 @@
         <v>80</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>80</v>
+        <v>243</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>80</v>
+        <v>428</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>80</v>
+        <v>429</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
@@ -9820,10 +9850,10 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>94</v>
@@ -9835,16 +9865,16 @@
         <v>106</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>80</v>
+        <v>431</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>80</v>
@@ -9853,18 +9883,18 @@
         <v>80</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>438</v>
+        <v>80</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9872,13 +9902,13 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>80</v>
@@ -9887,20 +9917,16 @@
         <v>95</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>249</v>
+        <v>435</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>443</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>80</v>
       </c>
@@ -9924,13 +9950,13 @@
         <v>80</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>154</v>
+        <v>80</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>80</v>
@@ -9948,13 +9974,13 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>80</v>
@@ -9963,36 +9989,36 @@
         <v>106</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>447</v>
+        <v>80</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>448</v>
+        <v>80</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10000,13 +10026,13 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>80</v>
@@ -10015,16 +10041,20 @@
         <v>95</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>398</v>
+        <v>108</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>444</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>80</v>
       </c>
@@ -10072,13 +10102,13 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="AG61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH61" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>80</v>
@@ -10087,16 +10117,16 @@
         <v>106</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>80</v>
+        <v>447</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>452</v>
+        <v>80</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>80</v>
@@ -10105,18 +10135,18 @@
         <v>80</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>80</v>
+        <v>449</v>
       </c>
       <c r="AR61" t="s" s="2">
-        <v>80</v>
+        <v>447</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10127,28 +10157,32 @@
         <v>81</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>108</v>
+        <v>260</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>109</v>
+        <v>451</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>454</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>80</v>
       </c>
@@ -10172,13 +10206,13 @@
         <v>80</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>80</v>
+        <v>154</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>80</v>
@@ -10196,84 +10230,82 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>111</v>
+        <v>450</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>80</v>
+        <v>455</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>80</v>
+        <v>456</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>112</v>
+        <v>457</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>80</v>
+        <v>458</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>80</v>
+        <v>459</v>
       </c>
       <c r="AR62" t="s" s="2">
-        <v>80</v>
+        <v>455</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>115</v>
+        <v>409</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>116</v>
+        <v>461</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>118</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>80</v>
@@ -10322,10 +10354,10 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>122</v>
+        <v>460</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>82</v>
@@ -10334,7 +10366,7 @@
         <v>80</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>80</v>
@@ -10343,10 +10375,10 @@
         <v>80</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>80</v>
+        <v>463</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>112</v>
+        <v>464</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>80</v>
@@ -10363,46 +10395,42 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>408</v>
+        <v>80</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>409</v>
+        <v>109</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>411</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>80</v>
       </c>
@@ -10450,19 +10478,19 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>412</v>
+        <v>111</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>80</v>
@@ -10474,7 +10502,7 @@
         <v>80</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>80</v>
@@ -10489,43 +10517,45 @@
         <v>80</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>458</v>
+        <v>115</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>459</v>
+        <v>116</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>117</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>80</v>
@@ -10574,19 +10604,19 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>457</v>
+        <v>122</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>80</v>
@@ -10595,62 +10625,66 @@
         <v>80</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>461</v>
+        <v>80</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>453</v>
+        <v>112</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>462</v>
+        <v>80</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>463</v>
+        <v>80</v>
       </c>
       <c r="AR65" t="s" s="2">
-        <v>464</v>
+        <v>80</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>80</v>
+        <v>419</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>109</v>
+        <v>420</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>421</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>422</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>80</v>
       </c>
@@ -10698,19 +10732,19 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>111</v>
+        <v>423</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>80</v>
+        <v>123</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>80</v>
@@ -10722,7 +10756,7 @@
         <v>80</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>112</v>
+        <v>194</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>80</v>
@@ -10737,45 +10771,43 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>115</v>
+        <v>469</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>116</v>
+        <v>470</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>118</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>80</v>
@@ -10812,31 +10844,31 @@
         <v>80</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>122</v>
+        <v>468</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>80</v>
@@ -10845,30 +10877,30 @@
         <v>80</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>80</v>
+        <v>472</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>112</v>
+        <v>464</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>80</v>
+        <v>473</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>80</v>
+        <v>474</v>
       </c>
       <c r="AR67" t="s" s="2">
-        <v>80</v>
+        <v>475</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10876,33 +10908,31 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>171</v>
+        <v>108</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>468</v>
+        <v>109</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>469</v>
+        <v>110</v>
       </c>
       <c r="N68" s="2"/>
-      <c r="O68" t="s" s="2">
-        <v>470</v>
-      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>80</v>
       </c>
@@ -10911,10 +10941,10 @@
         <v>80</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>471</v>
+        <v>80</v>
       </c>
       <c r="T68" t="s" s="2">
-        <v>472</v>
+        <v>80</v>
       </c>
       <c r="U68" t="s" s="2">
         <v>80</v>
@@ -10926,13 +10956,13 @@
         <v>80</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>232</v>
+        <v>80</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>473</v>
+        <v>80</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>474</v>
+        <v>80</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>80</v>
@@ -10950,7 +10980,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>475</v>
+        <v>111</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10962,10 +10992,10 @@
         <v>80</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>476</v>
+        <v>80</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>80</v>
@@ -10974,61 +11004,61 @@
         <v>80</v>
       </c>
       <c r="AN68" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AR68" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="AO68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ68" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="AR68" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s" s="2">
-        <v>479</v>
-      </c>
       <c r="B69" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>171</v>
+        <v>115</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>480</v>
+        <v>116</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" t="s" s="2">
-        <v>482</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>80</v>
       </c>
@@ -11040,7 +11070,7 @@
         <v>80</v>
       </c>
       <c r="T69" t="s" s="2">
-        <v>483</v>
+        <v>80</v>
       </c>
       <c r="U69" t="s" s="2">
         <v>80</v>
@@ -11052,46 +11082,46 @@
         <v>80</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>175</v>
+        <v>80</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>176</v>
+        <v>80</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>177</v>
+        <v>80</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>484</v>
+        <v>122</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>485</v>
+        <v>80</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>80</v>
@@ -11100,7 +11130,7 @@
         <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>486</v>
+        <v>112</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>80</v>
@@ -11115,12 +11145,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11128,34 +11158,32 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>488</v>
+        <v>171</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>491</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>492</v>
+        <v>481</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>80</v>
@@ -11165,10 +11193,10 @@
         <v>80</v>
       </c>
       <c r="S70" t="s" s="2">
-        <v>80</v>
+        <v>482</v>
       </c>
       <c r="T70" t="s" s="2">
-        <v>80</v>
+        <v>483</v>
       </c>
       <c r="U70" t="s" s="2">
         <v>80</v>
@@ -11180,13 +11208,13 @@
         <v>80</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>80</v>
+        <v>243</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>80</v>
+        <v>484</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>80</v>
+        <v>485</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>80</v>
@@ -11204,7 +11232,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -11219,7 +11247,7 @@
         <v>106</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>80</v>
+        <v>487</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>80</v>
@@ -11228,7 +11256,7 @@
         <v>80</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>80</v>
@@ -11237,7 +11265,7 @@
         <v>80</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="AR70" t="s" s="2">
         <v>80</v>
@@ -11245,10 +11273,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11256,7 +11284,7 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>94</v>
@@ -11271,19 +11299,17 @@
         <v>95</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>497</v>
+        <v>171</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>500</v>
-      </c>
+        <v>492</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>80</v>
@@ -11296,7 +11322,7 @@
         <v>80</v>
       </c>
       <c r="T71" t="s" s="2">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="U71" t="s" s="2">
         <v>80</v>
@@ -11308,13 +11334,13 @@
         <v>80</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>80</v>
+        <v>176</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>80</v>
+        <v>177</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>80</v>
@@ -11332,7 +11358,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -11347,7 +11373,7 @@
         <v>106</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>80</v>
@@ -11356,7 +11382,7 @@
         <v>80</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>80</v>
@@ -11365,7 +11391,7 @@
         <v>80</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>506</v>
+        <v>80</v>
       </c>
       <c r="AR71" t="s" s="2">
         <v>80</v>
@@ -11373,10 +11399,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11387,7 +11413,7 @@
         <v>81</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>80</v>
@@ -11396,22 +11422,22 @@
         <v>80</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>80</v>
@@ -11460,7 +11486,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11475,7 +11501,7 @@
         <v>106</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>514</v>
+        <v>80</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>80</v>
@@ -11484,7 +11510,7 @@
         <v>80</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>80</v>
@@ -11493,7 +11519,7 @@
         <v>80</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>80</v>
+        <v>506</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>80</v>
@@ -11501,10 +11527,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11512,7 +11538,7 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>94</v>
@@ -11527,19 +11553,19 @@
         <v>95</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>488</v>
+        <v>508</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>80</v>
@@ -11552,7 +11578,7 @@
         <v>80</v>
       </c>
       <c r="T73" t="s" s="2">
-        <v>80</v>
+        <v>513</v>
       </c>
       <c r="U73" t="s" s="2">
         <v>80</v>
@@ -11588,7 +11614,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11603,7 +11629,7 @@
         <v>106</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>80</v>
@@ -11612,7 +11638,7 @@
         <v>80</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>80</v>
@@ -11621,18 +11647,18 @@
         <v>80</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>80</v>
+        <v>517</v>
       </c>
       <c r="AR73" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11646,7 +11672,7 @@
         <v>94</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>80</v>
@@ -11655,17 +11681,19 @@
         <v>95</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>108</v>
+        <v>519</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="N74" s="2"/>
+        <v>521</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>522</v>
+      </c>
       <c r="O74" t="s" s="2">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>80</v>
@@ -11678,7 +11706,7 @@
         <v>80</v>
       </c>
       <c r="T74" t="s" s="2">
-        <v>528</v>
+        <v>80</v>
       </c>
       <c r="U74" t="s" s="2">
         <v>80</v>
@@ -11714,7 +11742,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11729,7 +11757,7 @@
         <v>106</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>80</v>
@@ -11738,7 +11766,7 @@
         <v>80</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>80</v>
@@ -11755,10 +11783,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11781,17 +11809,19 @@
         <v>95</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>533</v>
+        <v>499</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>529</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>530</v>
+      </c>
       <c r="O75" t="s" s="2">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>80</v>
@@ -11840,7 +11870,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11855,7 +11885,7 @@
         <v>106</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>80</v>
@@ -11864,7 +11894,7 @@
         <v>80</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>515</v>
+        <v>534</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>80</v>
@@ -11881,10 +11911,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11907,18 +11937,18 @@
         <v>95</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>149</v>
+        <v>108</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="O76" s="2"/>
+        <v>537</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" t="s" s="2">
+        <v>538</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>80</v>
       </c>
@@ -11930,7 +11960,7 @@
         <v>80</v>
       </c>
       <c r="T76" t="s" s="2">
-        <v>80</v>
+        <v>539</v>
       </c>
       <c r="U76" t="s" s="2">
         <v>80</v>
@@ -11942,11 +11972,13 @@
         <v>80</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="Y76" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z76" t="s" s="2">
-        <v>543</v>
+        <v>80</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>80</v>
@@ -11964,7 +11996,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11979,19 +12011,19 @@
         <v>106</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>545</v>
+        <v>80</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>453</v>
+        <v>542</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>546</v>
+        <v>80</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>80</v>
@@ -12000,15 +12032,15 @@
         <v>80</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>544</v>
+        <v>80</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12016,7 +12048,7 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>94</v>
@@ -12031,18 +12063,18 @@
         <v>95</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>398</v>
+        <v>544</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="O77" s="2"/>
+        <v>546</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" t="s" s="2">
+        <v>547</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>80</v>
       </c>
@@ -12090,7 +12122,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -12105,7 +12137,7 @@
         <v>106</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>80</v>
+        <v>549</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>80</v>
@@ -12114,7 +12146,7 @@
         <v>80</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>551</v>
+        <v>526</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>80</v>
@@ -12129,12 +12161,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12148,24 +12180,26 @@
         <v>94</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>108</v>
+        <v>149</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>109</v>
+        <v>551</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>552</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>553</v>
+      </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>80</v>
@@ -12190,13 +12224,11 @@
         <v>80</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>80</v>
+        <v>554</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>80</v>
@@ -12214,7 +12246,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>111</v>
+        <v>550</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -12226,22 +12258,22 @@
         <v>80</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>80</v>
+        <v>555</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>80</v>
+        <v>556</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>112</v>
+        <v>464</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>80</v>
+        <v>557</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>80</v>
@@ -12250,47 +12282,47 @@
         <v>80</v>
       </c>
       <c r="AR78" t="s" s="2">
-        <v>80</v>
+        <v>555</v>
       </c>
     </row>
-    <row r="79" hidden="true">
+    <row r="79">
       <c r="A79" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>115</v>
+        <v>409</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>116</v>
+        <v>559</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>117</v>
+        <v>560</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>118</v>
+        <v>561</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -12340,19 +12372,19 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>122</v>
+        <v>558</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>80</v>
@@ -12364,7 +12396,7 @@
         <v>80</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>112</v>
+        <v>562</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>80</v>
@@ -12381,46 +12413,42 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>554</v>
+        <v>563</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>554</v>
+        <v>563</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>408</v>
+        <v>80</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>409</v>
+        <v>109</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>411</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>80</v>
       </c>
@@ -12468,19 +12496,19 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>412</v>
+        <v>111</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>80</v>
@@ -12492,7 +12520,7 @@
         <v>80</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>80</v>
@@ -12509,14 +12537,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>555</v>
+        <v>564</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>555</v>
+        <v>564</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -12535,15 +12563,17 @@
         <v>80</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>556</v>
+        <v>115</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>557</v>
+        <v>116</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="N81" s="2"/>
+        <v>117</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>80</v>
@@ -12592,7 +12622,7 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>555</v>
+        <v>122</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12604,25 +12634,25 @@
         <v>80</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>559</v>
+        <v>80</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>560</v>
+        <v>80</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>561</v>
+        <v>80</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>562</v>
+        <v>112</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>563</v>
+        <v>80</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>80</v>
@@ -12633,14 +12663,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>80</v>
+        <v>419</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -12653,24 +12683,26 @@
         <v>80</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>249</v>
+        <v>115</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>565</v>
+        <v>420</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>566</v>
+        <v>421</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="O82" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>422</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>80</v>
       </c>
@@ -12694,13 +12726,13 @@
         <v>80</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>568</v>
+        <v>80</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>569</v>
+        <v>80</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>80</v>
@@ -12718,7 +12750,7 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>564</v>
+        <v>423</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12730,19 +12762,19 @@
         <v>80</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>570</v>
+        <v>80</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>571</v>
+        <v>80</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>572</v>
+        <v>194</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>80</v>
@@ -12754,15 +12786,15 @@
         <v>80</v>
       </c>
       <c r="AR82" t="s" s="2">
-        <v>570</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12773,25 +12805,25 @@
         <v>81</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12842,13 +12874,13 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>80</v>
@@ -12857,36 +12889,36 @@
         <v>106</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>80</v>
+        <v>570</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>80</v>
+        <v>571</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>579</v>
+        <v>80</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>80</v>
+        <v>574</v>
       </c>
       <c r="AQ83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AR83" t="s" s="2">
-        <v>580</v>
+        <v>80</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12897,7 +12929,7 @@
         <v>81</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>80</v>
@@ -12909,15 +12941,17 @@
         <v>80</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>108</v>
+        <v>260</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>109</v>
+        <v>576</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>577</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>578</v>
+      </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>80</v>
@@ -12942,13 +12976,13 @@
         <v>80</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>80</v>
+        <v>579</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>80</v>
+        <v>580</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>80</v>
@@ -12966,31 +13000,31 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>111</v>
+        <v>575</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>80</v>
+        <v>581</v>
       </c>
       <c r="AL84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>80</v>
+        <v>582</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>112</v>
+        <v>583</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>80</v>
@@ -13002,48 +13036,46 @@
         <v>80</v>
       </c>
       <c r="AR84" t="s" s="2">
-        <v>80</v>
+        <v>581</v>
       </c>
     </row>
-    <row r="85" hidden="true">
+    <row r="85">
       <c r="A85" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>115</v>
+        <v>585</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>116</v>
+        <v>586</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>118</v>
-      </c>
+        <v>587</v>
+      </c>
+      <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>80</v>
@@ -13080,31 +13112,31 @@
         <v>80</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>122</v>
+        <v>584</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>80</v>
@@ -13113,13 +13145,13 @@
         <v>80</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>80</v>
+        <v>588</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>112</v>
+        <v>589</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>80</v>
+        <v>590</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>80</v>
@@ -13128,15 +13160,15 @@
         <v>80</v>
       </c>
       <c r="AR85" t="s" s="2">
-        <v>80</v>
+        <v>591</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>583</v>
+        <v>592</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>583</v>
+        <v>592</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13156,20 +13188,18 @@
         <v>80</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>533</v>
+        <v>108</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>584</v>
+        <v>109</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>586</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>80</v>
@@ -13218,7 +13248,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>587</v>
+        <v>111</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -13227,13 +13257,13 @@
         <v>94</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>588</v>
+        <v>80</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>589</v>
+        <v>80</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>80</v>
@@ -13242,7 +13272,7 @@
         <v>80</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>590</v>
+        <v>112</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>80</v>
@@ -13251,7 +13281,7 @@
         <v>80</v>
       </c>
       <c r="AQ86" t="s" s="2">
-        <v>591</v>
+        <v>80</v>
       </c>
       <c r="AR86" t="s" s="2">
         <v>80</v>
@@ -13259,21 +13289,21 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>80</v>
@@ -13282,27 +13312,25 @@
         <v>80</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>533</v>
+        <v>115</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>593</v>
+        <v>116</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>594</v>
+        <v>117</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>595</v>
+        <v>118</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q87" t="s" s="2">
-        <v>596</v>
-      </c>
+      <c r="Q87" s="2"/>
       <c r="R87" t="s" s="2">
         <v>80</v>
       </c>
@@ -13334,34 +13362,34 @@
         <v>80</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>597</v>
+        <v>122</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>588</v>
+        <v>80</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>598</v>
+        <v>80</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>80</v>
@@ -13370,7 +13398,7 @@
         <v>80</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>599</v>
+        <v>112</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>80</v>
@@ -13379,18 +13407,18 @@
         <v>80</v>
       </c>
       <c r="AQ87" t="s" s="2">
-        <v>600</v>
+        <v>80</v>
       </c>
       <c r="AR87" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13404,24 +13432,26 @@
         <v>94</v>
       </c>
       <c r="H88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J88" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="I88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J88" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K88" t="s" s="2">
-        <v>249</v>
+        <v>544</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="N88" s="2"/>
+        <v>596</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>597</v>
+      </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>80</v>
@@ -13446,13 +13476,13 @@
         <v>80</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>604</v>
+        <v>80</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>605</v>
+        <v>80</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>80</v>
@@ -13470,7 +13500,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13479,42 +13509,42 @@
         <v>94</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>80</v>
+        <v>599</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>607</v>
+        <v>80</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>609</v>
+        <v>80</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ88" t="s" s="2">
-        <v>80</v>
+        <v>602</v>
       </c>
       <c r="AR88" t="s" s="2">
-        <v>606</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13528,33 +13558,33 @@
         <v>94</v>
       </c>
       <c r="H89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J89" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="I89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J89" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K89" t="s" s="2">
-        <v>249</v>
+        <v>544</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>614</v>
-      </c>
+        <v>606</v>
+      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q89" s="2"/>
+      <c r="Q89" t="s" s="2">
+        <v>607</v>
+      </c>
       <c r="R89" t="s" s="2">
         <v>80</v>
       </c>
@@ -13574,13 +13604,13 @@
         <v>80</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>615</v>
+        <v>80</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>616</v>
+        <v>80</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>80</v>
@@ -13598,7 +13628,7 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13607,42 +13637,42 @@
         <v>94</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>80</v>
+        <v>599</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>607</v>
+        <v>80</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>607</v>
+        <v>80</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ89" t="s" s="2">
-        <v>80</v>
+        <v>611</v>
       </c>
       <c r="AR89" t="s" s="2">
-        <v>617</v>
+        <v>80</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13665,13 +13695,13 @@
         <v>80</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>619</v>
+        <v>260</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -13698,13 +13728,13 @@
         <v>80</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>80</v>
+        <v>615</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>80</v>
+        <v>616</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>80</v>
@@ -13722,7 +13752,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13737,19 +13767,19 @@
         <v>106</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>80</v>
+        <v>617</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>353</v>
+        <v>618</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>354</v>
+        <v>619</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>355</v>
+        <v>620</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>80</v>
@@ -13758,15 +13788,15 @@
         <v>80</v>
       </c>
       <c r="AR90" t="s" s="2">
-        <v>622</v>
+        <v>617</v>
       </c>
     </row>
-    <row r="91" hidden="true">
+    <row r="91">
       <c r="A91" t="s" s="2">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13780,7 +13810,7 @@
         <v>94</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>80</v>
@@ -13789,16 +13819,20 @@
         <v>80</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>108</v>
+        <v>260</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>109</v>
+        <v>622</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
+        <v>623</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>625</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>80</v>
       </c>
@@ -13822,13 +13856,13 @@
         <v>80</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>80</v>
+        <v>626</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>80</v>
+        <v>627</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>80</v>
@@ -13846,7 +13880,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>111</v>
+        <v>621</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13858,22 +13892,22 @@
         <v>80</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>80</v>
+        <v>628</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>80</v>
+        <v>618</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>112</v>
+        <v>619</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>80</v>
+        <v>618</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>80</v>
@@ -13882,29 +13916,29 @@
         <v>80</v>
       </c>
       <c r="AR91" t="s" s="2">
-        <v>80</v>
+        <v>628</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>80</v>
@@ -13913,17 +13947,15 @@
         <v>80</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>115</v>
+        <v>630</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>116</v>
+        <v>631</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>118</v>
-      </c>
+        <v>632</v>
+      </c>
+      <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>80</v>
@@ -13960,31 +13992,31 @@
         <v>80</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AC92" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AD92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>122</v>
+        <v>629</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>80</v>
@@ -13993,13 +14025,13 @@
         <v>80</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>80</v>
+        <v>364</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>112</v>
+        <v>365</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>80</v>
+        <v>366</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>80</v>
@@ -14008,15 +14040,15 @@
         <v>80</v>
       </c>
       <c r="AR92" t="s" s="2">
-        <v>80</v>
+        <v>633</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>625</v>
+        <v>634</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>625</v>
+        <v>634</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14036,20 +14068,18 @@
         <v>80</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="K93" t="s" s="2">
         <v>108</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>626</v>
+        <v>109</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>628</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N93" s="2"/>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>80</v>
@@ -14098,7 +14128,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>629</v>
+        <v>111</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -14107,13 +14137,13 @@
         <v>94</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>630</v>
+        <v>80</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>631</v>
+        <v>80</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>80</v>
@@ -14122,7 +14152,7 @@
         <v>80</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>80</v>
@@ -14139,21 +14169,21 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>80</v>
@@ -14162,19 +14192,19 @@
         <v>80</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>633</v>
+        <v>116</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>634</v>
+        <v>117</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>635</v>
+        <v>118</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -14200,43 +14230,43 @@
         <v>80</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>636</v>
+        <v>80</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>637</v>
+        <v>80</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AC94" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AD94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>638</v>
+        <v>122</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>80</v>
@@ -14248,7 +14278,7 @@
         <v>80</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>80</v>
@@ -14265,10 +14295,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14291,16 +14321,16 @@
         <v>95</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>214</v>
+        <v>108</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -14350,7 +14380,7 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -14359,13 +14389,13 @@
         <v>94</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>80</v>
+        <v>641</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>80</v>
@@ -14374,7 +14404,7 @@
         <v>80</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>645</v>
+        <v>194</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>80</v>
@@ -14391,10 +14421,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14417,16 +14447,16 @@
         <v>95</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14452,13 +14482,13 @@
         <v>80</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>80</v>
+        <v>647</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>80</v>
+        <v>648</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>80</v>
@@ -14476,7 +14506,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -14517,10 +14547,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14531,7 +14561,7 @@
         <v>81</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>80</v>
@@ -14540,19 +14570,19 @@
         <v>80</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>652</v>
       </c>
-      <c r="L97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>653</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>655</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14602,13 +14632,13 @@
         <v>80</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>80</v>
@@ -14617,32 +14647,284 @@
         <v>106</v>
       </c>
       <c r="AK97" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN97" t="s" s="2">
         <v>656</v>
       </c>
-      <c r="AL97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM97" t="s" s="2">
+      <c r="AO97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AR97" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
         <v>657</v>
       </c>
-      <c r="AN97" t="s" s="2">
+      <c r="B98" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L98" t="s" s="2">
         <v>658</v>
       </c>
-      <c r="AO97" t="s" s="2">
+      <c r="M98" t="s" s="2">
         <v>659</v>
       </c>
-      <c r="AP97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AR97" t="s" s="2">
+      <c r="N98" t="s" s="2">
         <v>660</v>
+      </c>
+      <c r="O98" s="2"/>
+      <c r="P98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AR98" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="99" hidden="true">
+      <c r="A99" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="O99" s="2"/>
+      <c r="P99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="AP99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AR99" t="s" s="2">
+        <v>671</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR97">
+  <autoFilter ref="A1:AR99">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -14652,7 +14934,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI96">
+  <conditionalFormatting sqref="A2:AI98">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/output/StructureDefinition-ReferenciaDocumental.xlsx
+++ b/output/StructureDefinition-ReferenciaDocumental.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T16:15:28-03:00</t>
+    <t>2026-10-22T10:20:43-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
